--- a/odk/forms/crop_sown_registry_prep.xlsx
+++ b/odk/forms/crop_sown_registry_prep.xlsx
@@ -661,1979 +661,2024 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="39" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="39" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="39" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="39" t="inlineStr">
         <is>
           <t>read_only</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="39" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="39" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="39" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="39" t="inlineStr">
         <is>
           <t>repeat_count</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="39" t="inlineStr">
         <is>
           <t>required_message</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>farmer_identity</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Farmer Identity</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="39" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>farmer_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Farmer ID</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="39" t="inlineStr">
         <is>
           <t>FR- followed by 12 digits, for example FR-123456789012</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="39" t="inlineStr">
         <is>
           <t>regex(., '^FR-[0-9]{12}$')</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="39" t="inlineStr">
         <is>
           <t>The Farmer ID must be FR- followed by 12 digits, for example FR-123456789012.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="39" t="inlineStr">
         <is>
           <t>Enter the Farmer ID.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>fayda_id_entered</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Fayda ID</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>The 16 digit FAN or the 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>regex(translate(., ' ', ''), '^([0-9]{12}|[0-9]{16})$')</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>The Fayda ID must be a 16 digit FAN or a 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="39" t="inlineStr">
         <is>
           <t>Enter the Fayda ID.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>fayda_id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="39" t="inlineStr">
         <is>
           <t>translate(${fayda_id_entered}, ' ', '')</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>production_season_info</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="39" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>crop_year</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>Crop Year</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>. = number(format-date(today(), '%Y'))</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>Only the current crop year is allowed.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>production_season</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="O9" s="39" t="inlineStr">
+        <is>
+          <t>Select the production season.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>cult_land_prep</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>Cultivation / Land Preparation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>is_plot_not_registered</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Plot not registered</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>land_info_id</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="O13" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>land_area</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Total Land Area (ha)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>. &gt; 0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>Total Land Area must be greater than 0.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="39" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O15" s="39" t="inlineStr">
+        <is>
+          <t>Select the season.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>start_gc</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Start GC</t>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>end_gc</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>End GC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>End Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>. &gt;= ${start_gc}</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="39" t="inlineStr">
         <is>
           <t>End date cannot be before Start date.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>start_month</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Start Month</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="39" t="inlineStr">
         <is>
           <t>format-date(${start_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>start_day</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="39" t="inlineStr">
         <is>
           <t>Start Day</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="39" t="inlineStr">
         <is>
           <t>format-date(${start_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>end_month</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>End Month</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="39" t="inlineStr">
         <is>
           <t>format-date(${end_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>end_day</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
         <is>
           <t>End Day</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="39" t="inlineStr">
         <is>
           <t>format-date(${end_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crop </t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O22" s="39" t="inlineStr">
+        <is>
+          <t>Select the crop.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>crop_category_id</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>Crop Category</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="39" t="inlineStr">
         <is>
           <t>instance('crop_name')/root/item[name=${crop_name_id}]/category</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>crop_category_name</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="39" t="inlineStr">
         <is>
           <t>instance('crop_name')/root/item[name=${crop_name_id}]/category_label</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>note_crop_category</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>Crop Category: ${crop_category_name}</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file crop_variety.csv</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>crop_variety_id</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>Crop Variety</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>local_name</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="39" t="inlineStr">
         <is>
           <t>Local Name</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>scientific_name</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>Scientific Name</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>select_one cropping_sys</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>cropping_system</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="39" t="inlineStr">
         <is>
           <t>Cropping System</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>collected_gc</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Actual Cultivated Date (GC)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>Actual Cultivated Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F30" s="39" t="inlineStr">
         <is>
           <t>. &gt;= ${start_gc} and . &lt;= ${end_gc}</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Actual Cultivated Date (GC) must be between Start GC and End GC.</t>
+      <c r="G30" s="39" t="inlineStr">
+        <is>
+          <t>Actual Cultivated Date (GC) must be between Start Date and End Date.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>actual_growth_duration</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="39" t="inlineStr">
         <is>
           <t>Actual Growth Duration (days)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="39" t="inlineStr">
         <is>
           <t>Growth Duration cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>actual_crop_area</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="39" t="inlineStr">
         <is>
           <t>Actual Crop Area (ha)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= ${land_area}</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="39" t="inlineStr">
         <is>
           <t>concat('Actual crop area cannot exceed total land area of ', ${land_area}, ' ha')</t>
         </is>
       </c>
+      <c r="O32" s="39" t="inlineStr">
+        <is>
+          <t>Enter the actual crop area (ha).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>actual_yield</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Actual Yield (quintal)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>Actual Yield (quintals)</t>
+        </is>
+      </c>
+      <c r="F33" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="39" t="inlineStr">
         <is>
           <t>Actual Yield cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>select_one cult_method</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>cultivated_by</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
         <is>
           <t>Cultivation Type</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="39" t="inlineStr">
         <is>
           <t>select_multiple land_prep_method</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>land_prep_method_ids</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Land Prep Methods</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>Land Preparation Methods</t>
+        </is>
+      </c>
+      <c r="K35" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>select_one seed_class</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>actual_seed_class</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>Seed Type</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>select_one seed_source</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>actual_seed_source</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="39" t="inlineStr">
         <is>
           <t>Seed Source</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file seed_variety.csv</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>seed_variety</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="39" t="inlineStr">
         <is>
           <t>Seed Variety</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>actual_seed_qty</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="39" t="inlineStr">
         <is>
           <t>Actual Seed Quantity (kg)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="39" t="inlineStr">
         <is>
           <t>Actual Seed Quantity cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>select_one fertilizer_type</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>actual_fertilizer_type</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="39" t="inlineStr">
         <is>
           <t>Actual Fertilizer Type</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>actual_fertilizer_qty</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>Actual Fertilizer Quantity (kg)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="39" t="inlineStr">
         <is>
           <t>Actual Fertilizer Quantity cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>select_one water_source</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>water_resource_id</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Water Resource</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>Water Source</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O42" s="39" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>select_one method</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>method_id</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Method</t>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>Irrigation Method</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>select_one frequency</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Frequency</t>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>surveyor_name</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>DA Name</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="C45" s="39" t="inlineStr">
+        <is>
+          <t>Development Agent Name</t>
+        </is>
+      </c>
+      <c r="F45" s="39" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G45" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>surveyor_mobile_number</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DA Mobile Number</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>Development Agent Mobile Number</t>
+        </is>
+      </c>
+      <c r="D46" s="39" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G46" s="39" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>supervisor_name</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="39" t="inlineStr">
         <is>
           <t>Supervisor Name</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="39" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G47" s="39" t="inlineStr">
+        <is>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>supervisor_mobile_number</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="39" t="inlineStr">
         <is>
           <t>Supervisor Mobile Number</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="D48" s="39" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G48" s="39" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="39" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="39" t="inlineStr">
         <is>
           <t>cluster_information</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="39" t="inlineStr">
         <is>
           <t>Cluster Information</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>cluster_land_info_id</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="39" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="39" t="inlineStr">
         <is>
           <t>. = ${land_info_id}</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="39" t="inlineStr">
         <is>
           <t>Land ID does not match the Land ID provided in Cultivation / Land Preparation. Please enter the correct Land ID.</t>
         </is>
       </c>
+      <c r="O50" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="39" t="inlineStr">
         <is>
           <t>cluster_name</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>FPC Name</t>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>cluster_season_id</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="39" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="39" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="39" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="39" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>cluster_start_gc</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Start GC</t>
+      <c r="C53" s="39" t="inlineStr">
+        <is>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>cluster_end_gc</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>End GC</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="C54" s="39" t="inlineStr">
+        <is>
+          <t>End Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F54" s="39" t="inlineStr">
         <is>
           <t>. &gt;= ${cluster_start_gc}</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="39" t="inlineStr">
         <is>
           <t>End date cannot be before Start date.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>cluster_start_month</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="39" t="inlineStr">
         <is>
           <t>Start Month</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="39" t="inlineStr">
         <is>
           <t>format-date(${cluster_start_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>cluster_start_day</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="39" t="inlineStr">
         <is>
           <t>Start Day</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="39" t="inlineStr">
         <is>
           <t>format-date(${cluster_start_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="39" t="inlineStr">
         <is>
           <t>cluster_end_month</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="39" t="inlineStr">
         <is>
           <t>End Month</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="39" t="inlineStr">
         <is>
           <t>format-date(${cluster_end_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>cluster_end_day</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="39" t="inlineStr">
         <is>
           <t>End Day</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="39" t="inlineStr">
         <is>
           <t>format-date(${cluster_end_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file region.csv</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="39" t="inlineStr">
         <is>
           <t>cluster_region_id</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="39" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file zone.csv</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>cluster_zone_id</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="39" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="39" t="inlineStr">
         <is>
           <t>parent=${cluster_region_id}</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file woreda.csv</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="39" t="inlineStr">
         <is>
           <t>cluster_woreda_id</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="39" t="inlineStr">
         <is>
           <t>Woreda</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="39" t="inlineStr">
         <is>
           <t>parent=${cluster_zone_id}</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="39" t="inlineStr">
         <is>
           <t>select_one_from_file kebele.csv</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>cluster_kebele_id</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="39" t="inlineStr">
         <is>
           <t>Kebele</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="39" t="inlineStr">
         <is>
           <t>parent=${cluster_woreda_id}</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>sub_kebele</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="39" t="inlineStr">
         <is>
           <t>Sub-Kebele</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="39" t="inlineStr">
         <is>
           <t>select_one agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>cluster_agro_ecological_zone</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="39" t="inlineStr">
         <is>
           <t>Agro Ecological Zone</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>remaining_land_area</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="39" t="inlineStr">
         <is>
           <t>Remaining Land Area</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="39" t="inlineStr">
         <is>
           <t>${land_area} - ${actual_crop_area}</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>cluster_area_timad</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="39" t="inlineStr">
         <is>
           <t>Total Cultivated Area (Timad)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="D66" s="39" t="inlineStr">
+        <is>
+          <t>One Timad is 0.25 hectare.</t>
+        </is>
+      </c>
+      <c r="F66" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0 and (. * 0.25) &lt;= ${remaining_land_area}</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="39" t="inlineStr">
         <is>
           <t>Total Cultivated Area cannot be negative or exceed the remaining available land area.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="39" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>cluster_area_hectare</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="39" t="inlineStr">
         <is>
           <t>if(${cluster_area_timad} != '', ${cluster_area_timad} * 0.25, 0)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>total_area_display</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="39" t="inlineStr">
         <is>
           <t>Total Cultivated Area (ha): ${cluster_area_hectare}</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="39" t="inlineStr">
         <is>
           <t>cluster_plan</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Actual Plan (ha)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="C69" s="39" t="inlineStr">
+        <is>
+          <t>Actual Planned Area (ha)</t>
+        </is>
+      </c>
+      <c r="F69" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= ${cluster_area_hectare}</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Plan (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
+      <c r="G69" s="39" t="inlineStr">
+        <is>
+          <t>Planned Area (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>cluster_collected_land_quintal</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Actual Collected Land (Quintal)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>Actual Collected Land (quintals)</t>
+        </is>
+      </c>
+      <c r="F70" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Actual Collected Land (Quintal) cannot be negative.</t>
+      <c r="G70" s="39" t="inlineStr">
+        <is>
+          <t>Actual Collected Land (quintals) cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="39" t="inlineStr">
         <is>
           <t>cluster_collected_quintal</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Actual Collected Quintal</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="C71" s="39" t="inlineStr">
+        <is>
+          <t>Actual Quantity Collected (quintals)</t>
+        </is>
+      </c>
+      <c r="F71" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Actual Collected Quintal cannot be negative.</t>
+      <c r="G71" s="39" t="inlineStr">
+        <is>
+          <t>Actual Quantity Collected cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="39" t="inlineStr">
         <is>
           <t>cluster_collected_by_combiner</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Actual Collected by Combiner (ha)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>Actual Area Collected by Combine Harvester (ha)</t>
+        </is>
+      </c>
+      <c r="F72" s="39" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= ${cluster_plan}</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Actual Collected by Combiner (ha) must be 0 or greater and cannot exceed Actual Plan (ha).</t>
+      <c r="G72" s="39" t="inlineStr">
+        <is>
+          <t>Actual Area Collected by Combine Harvester (ha) must be 0 or greater and cannot exceed Actual Planned Area (ha).</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="39" t="inlineStr">
         <is>
           <t>select_one water_source</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>cluster_water_resource_id</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Water Resource</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>Water Source</t>
+        </is>
+      </c>
+      <c r="E73" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O73" s="39" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="39" t="inlineStr">
         <is>
           <t>select_one method</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="39" t="inlineStr">
         <is>
           <t>cluster_method_id</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Method</t>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>Irrigation Method</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="39" t="inlineStr">
         <is>
           <t>select_one frequency</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="39" t="inlineStr">
         <is>
           <t>cluster_frequency</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Frequency</t>
+      <c r="C75" s="39" t="inlineStr">
+        <is>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="39" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>cluster_smallholders</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="39" t="inlineStr">
         <is>
           <t>Number of Smallholders</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="39" t="inlineStr">
         <is>
           <t>cluster_surveyor_name</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>DA Name</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="C77" s="39" t="inlineStr">
+        <is>
+          <t>Development Agent Name</t>
+        </is>
+      </c>
+      <c r="F77" s="39" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G77" s="39" t="inlineStr">
+        <is>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>cluster_surveyor_mobile_number</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>DA Mobile Number</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>Development Agent Mobile Number</t>
+        </is>
+      </c>
+      <c r="D78" s="39" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F78" s="39" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G78" s="39" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="39" t="inlineStr">
         <is>
           <t>cluster_supervisor_name</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="39" t="inlineStr">
         <is>
           <t>Supervisor Name</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="39" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G79" s="39" t="inlineStr">
+        <is>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
         <is>
           <t>cluster_supervisor_mobile_number</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="39" t="inlineStr">
         <is>
           <t>Supervisor Mobile Number</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="D80" s="39" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F80" s="39" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G80" s="39" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="39" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="39" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
@@ -2654,1130 +2699,1130 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="39" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="39" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>yes_only</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>cropping_sys</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>mono_cropping</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>Mono-cropping</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>cropping_sys</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>inter_cropping</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Inter-cropping</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>government</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>Government / Woreda Agriculture Office</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>cooperative</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>Agricultural Cooperative / Union</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>private</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>Private Seed Enterprise</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Farmer-to-Farmer Exchange /Saved Seed</t>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>Farmer-to-Farmer Exchange / Saved Seed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>seed_class</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>seed_class</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>improved</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>Improved</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>rainfed</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>Rainfed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>river</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>River</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>pond</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>Pond</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Well</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>borehole</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>Borehole</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>irrigation_scheme</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>Irrigation Scheme</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>water_harvesting_structure</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Water Harvesting Structure</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>surface_flood</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="39" t="inlineStr">
         <is>
           <t>Surface / Flood</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>sprinkler</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>Sprinkler</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>drip</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
         <is>
           <t>Drip</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="39" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="39" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>bi-weekly</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bi-weekly</t>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Every two weeks</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="39" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>as_needed</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>As Needed</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>urea</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>Urea</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>nps</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nps</t>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>NPS</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>npsb</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Npsb</t>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>NPSB</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>dap</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Dap</t>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>DAP</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>compost</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
         <is>
           <t>Compost</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>manure</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="39" t="inlineStr">
         <is>
           <t>Manure</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>blended</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>Blended</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="39" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>oxen_tillage</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="39" t="inlineStr">
         <is>
           <t>Oxen Tillage</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>equine_other</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="39" t="inlineStr">
         <is>
           <t>Equine/Other Animals</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>tractor_ploughing</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="39" t="inlineStr">
         <is>
           <t>Tractor Ploughing</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>power_tiller</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>Power Tiller</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>combine_harvester</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="39" t="inlineStr">
         <is>
           <t>Combine Harvester</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>thrashing_machine</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Thrashing Machine</t>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>Threshing Machine</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>family_labor</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Family Labor</t>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>Family Labour</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>debo_jigi</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="39" t="inlineStr">
         <is>
           <t>Debo / Jigi</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>hired_labor</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Hired Labor</t>
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>Hired Labour</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>tractor_oxen</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="39" t="inlineStr">
         <is>
           <t>Tractor Primary Tillage + Oxen Secondary Tillage</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>oxen_manual</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="39" t="inlineStr">
         <is>
           <t>Oxen Ploughing + Manual Row Seeding</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="39" t="inlineStr">
         <is>
           <t>traditional_maresha_ploughing</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="39" t="inlineStr">
         <is>
           <t>Traditional Maresha Ploughing</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>tractor_disc/moldboard_ploughing</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tractor Disc/Moldboard Ploughing</t>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>Tractor Disc / Moldboard Ploughing</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="39" t="inlineStr">
         <is>
           <t>manual_digging</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="39" t="inlineStr">
         <is>
           <t>Manual Digging</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>shilshalo</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="39" t="inlineStr">
         <is>
           <t>Shilshalo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>ridging_furrowing</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="39" t="inlineStr">
         <is>
           <t>Ridging / Furrowing</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>manual_leveling</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Manual leveling</t>
+      <c r="C54" s="39" t="inlineStr">
+        <is>
+          <t>Manual Levelling</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>minimum_tillage</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="39" t="inlineStr">
         <is>
           <t>Minimum Tillage</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>soil_water_conservation_structures</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="39" t="inlineStr">
         <is>
           <t>Soil &amp; Water Conservation Structures</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="39" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="39" t="inlineStr">
         <is>
           <t>biological_mulching</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="39" t="inlineStr">
         <is>
           <t>Biological Mulching</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="39" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>SEASON_MEHER</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="39" t="inlineStr">
         <is>
           <t>Meher (main rains)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="39" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="39" t="inlineStr">
         <is>
           <t>SEASON_BELG</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="39" t="inlineStr">
         <is>
           <t>Belg (short rains)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>SEASON_IRRIGATION</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="39" t="inlineStr">
         <is>
           <t>Irrigation (dry season)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="39" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="39" t="inlineStr">
         <is>
           <t>AEZ_BEREHA</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="39" t="inlineStr">
         <is>
           <t>Bereha (hot lowland)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="39" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>AEZ_KOLLA</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="39" t="inlineStr">
         <is>
           <t>Kolla (lowland)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="39" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>AEZ_WEYNA_DEGA</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="39" t="inlineStr">
         <is>
           <t>Weyna Dega (midland)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="39" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>AEZ_DEGA</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="39" t="inlineStr">
         <is>
           <t>Dega (highland)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="39" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>AEZ_WURCH</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="39" t="inlineStr">
         <is>
           <t>Wurch (cold highland)</t>
         </is>
@@ -3798,64 +3843,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>style</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>allow_choice_duplicates</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CSR – 2. Cultivation &amp; Land</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Crop Sown Registry - 2. Cultivation and Land Preparation</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>crop_sown_registry_prep</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026.10.30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>2026.10.31</t>
+        </is>
+      </c>
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>English (en)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/odk/forms/crop_sown_registry_prep.xlsx
+++ b/odk/forms/crop_sown_registry_prep.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G30" s="39" t="inlineStr">
         <is>
-          <t>Actual Cultivated Date (GC) must be between Start Date and End Date.</t>
+          <t>Actual Cultivated Date must be between Start Date and End Date.</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C2" s="39" t="inlineStr">
         <is>
-          <t>2026.10.31</t>
+          <t>2026.10.31.1</t>
         </is>
       </c>
       <c r="D2" s="39" t="inlineStr">

--- a/odk/forms/crop_sown_registry_prep.xlsx
+++ b/odk/forms/crop_sown_registry_prep.xlsx
@@ -657,2028 +657,2006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" s="39" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="H1" s="39" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" s="39" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" s="39" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>read_only</t>
         </is>
       </c>
-      <c r="K1" s="39" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="L1" s="39" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" s="39" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" s="39" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>repeat_count</t>
         </is>
       </c>
-      <c r="O1" s="39" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>required_message</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>farmer_identity</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Farmer Identity</t>
         </is>
       </c>
-      <c r="K2" s="39" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>farmer_id</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Farmer ID</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FR- followed by 12 digits, for example FR-123456789012</t>
         </is>
       </c>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" s="39" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>regex(., '^FR-[0-9]{12}$')</t>
         </is>
       </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>The Farmer ID must be FR- followed by 12 digits, for example FR-123456789012.</t>
         </is>
       </c>
-      <c r="O3" s="39" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Enter the Farmer ID.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>fayda_id_entered</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Fayda ID</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>The 16 digit FAN or the 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>regex(translate(., ' ', ''), '^([0-9]{12}|[0-9]{16})$')</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>The Fayda ID must be a 16 digit FAN or a 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="O4" s="39" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Enter the Fayda ID.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>fayda_id</t>
         </is>
       </c>
-      <c r="I5" s="39" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>translate(${fayda_id_entered}, ' ', '')</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>production_season_info</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="K7" s="39" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>crop_year</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Crop Year</t>
         </is>
       </c>
-      <c r="F8" s="39" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>. = number(format-date(today(), '%Y'))</t>
         </is>
       </c>
-      <c r="G8" s="39" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Only the current crop year is allowed.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>production_season</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="E9" s="39" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O9" s="39" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Select the production season.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>cult_land_prep</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cultivation / Land Preparation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>is_plot_not_registered</t>
         </is>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Plot not registered</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>land_info_id</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E13" s="39" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O13" s="39" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Enter the Land ID.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>land_area</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Total Land Area (ha)</t>
         </is>
       </c>
-      <c r="F14" s="39" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>. &gt; 0</t>
         </is>
       </c>
-      <c r="G14" s="39" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Total Land Area must be greater than 0.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="E15" s="39" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F15" s="39" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G15" s="39" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
-      <c r="K15" s="39" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="O15" s="39" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Select the season.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>start_gc</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>end_gc</t>
         </is>
       </c>
-      <c r="C17" s="39" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>End Date (Gregorian calendar)</t>
         </is>
       </c>
-      <c r="F17" s="39" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>. &gt;= ${start_gc}</t>
         </is>
       </c>
-      <c r="G17" s="39" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>End date cannot be before Start date.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>start_month</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Start Month</t>
         </is>
       </c>
-      <c r="I18" s="39" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>format-date(${start_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J18" s="39" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>start_day</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Start Day</t>
         </is>
       </c>
-      <c r="I19" s="39" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>format-date(${start_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J19" s="39" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>end_month</t>
         </is>
       </c>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>End Month</t>
         </is>
       </c>
-      <c r="I20" s="39" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>format-date(${end_gc}, '%m')</t>
         </is>
       </c>
-      <c r="J20" s="39" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>end_day</t>
         </is>
       </c>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>End Day</t>
         </is>
       </c>
-      <c r="I21" s="39" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>format-date(${end_gc}, '%d')</t>
         </is>
       </c>
-      <c r="J21" s="39" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Crop</t>
         </is>
       </c>
-      <c r="E22" s="39" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K22" s="39" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="O22" s="39" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Select the crop.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>crop_category_id</t>
         </is>
       </c>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Crop Category</t>
         </is>
       </c>
-      <c r="I23" s="39" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>instance('crop_name')/root/item[name=${crop_name_id}]/category</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>crop_category_name</t>
         </is>
       </c>
-      <c r="I24" s="39" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>instance('crop_name')/root/item[name=${crop_name_id}]/category_label</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>note_crop_category</t>
         </is>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Crop Category: ${crop_category_name}</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file crop_variety.csv</t>
-        </is>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t>crop_variety_id</t>
-        </is>
-      </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>Crop Variety</t>
-        </is>
-      </c>
-      <c r="K26" s="39" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>local_name</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Local Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>scientific_name</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Scientific Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>select_one cropping_sys</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cropping_system</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cropping System</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>collected_gc</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Actual Cultivated Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>. &gt;= ${start_gc} and . &lt;= ${end_gc}</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actual Cultivated Date must be between Start Date and End Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>actual_growth_duration</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Actual Growth Duration (days)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Growth Duration cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>actual_crop_area</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Actual Crop Area (ha)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${land_area}</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>concat('Actual crop area cannot exceed total land area of ', ${land_area}, ' ha')</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Enter the actual crop area (ha).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>actual_yield</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Actual Yield (quintals)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actual Yield cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>select_one cult_method</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cultivated_by</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cultivation Type</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>select_multiple land_prep_method</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>land_prep_method_ids</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Land Preparation Methods</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>select_one seed_class</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>actual_seed_class</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seed Type</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>select_one seed_source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>actual_seed_source</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Seed Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>select_one_from_file seed_variety.csv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>seed_variety</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>actual_seed_qty</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Actual Seed Quantity (kg)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actual Seed Quantity cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>select_one fertilizer_type</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>actual_fertilizer_type</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Actual Fertilizer Type</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>actual_fertilizer_qty</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Actual Fertilizer Quantity (kg)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Actual Fertilizer Quantity cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>select_one water_source</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>water_resource_id</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Water Source</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>select_one method</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>method_id</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Irrigation Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>select_one frequency</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Irrigation Frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>local_name</t>
-        </is>
-      </c>
-      <c r="C27" s="39" t="inlineStr">
-        <is>
-          <t>Local Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>surveyor_name</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Development Agent Name</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t>scientific_name</t>
-        </is>
-      </c>
-      <c r="C28" s="39" t="inlineStr">
-        <is>
-          <t>Scientific Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="39" t="inlineStr">
-        <is>
-          <t>select_one cropping_sys</t>
-        </is>
-      </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>cropping_system</t>
-        </is>
-      </c>
-      <c r="C29" s="39" t="inlineStr">
-        <is>
-          <t>Cropping System</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>surveyor_mobile_number</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Development Agent Mobile Number</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>supervisor_name</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Supervisor Name</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>supervisor_mobile_number</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Supervisor Mobile Number</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>begin_repeat</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cluster_information</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cluster Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cluster_land_info_id</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Land ID</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>. = ${land_info_id}</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Land ID does not match the Land ID provided in Cultivation / Land Preparation. Please enter the correct Land ID.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Farmer Production Cluster (FPC) Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>select_one crop_season</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cluster_season_id</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>. = ${production_season}</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Season must match the Production Season selected earlier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>collected_gc</t>
-        </is>
-      </c>
-      <c r="C30" s="39" t="inlineStr">
-        <is>
-          <t>Actual Cultivated Date (Gregorian calendar)</t>
-        </is>
-      </c>
-      <c r="F30" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= ${start_gc} and . &lt;= ${end_gc}</t>
-        </is>
-      </c>
-      <c r="G30" s="39" t="inlineStr">
-        <is>
-          <t>Actual Cultivated Date must be between Start Date and End Date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>cluster_start_gc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Start Date (Gregorian calendar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cluster_end_gc</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>End Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>. &gt;= ${cluster_start_gc}</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>End date cannot be before Start date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cluster_start_month</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Start Month</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>format-date(${cluster_start_gc}, '%m')</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>cluster_start_day</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Start Day</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>format-date(${cluster_start_gc}, '%d')</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cluster_end_month</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>End Month</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>format-date(${cluster_end_gc}, '%m')</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>cluster_end_day</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>End Day</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>format-date(${cluster_end_gc}, '%d')</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>select_one_from_file region.csv</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>cluster_region_id</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>select_one_from_file zone.csv</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>cluster_zone_id</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>parent=${cluster_region_id}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>select_one_from_file woreda.csv</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cluster_woreda_id</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Woreda</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>parent=${cluster_zone_id}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>select_one_from_file kebele.csv</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>cluster_kebele_id</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kebele</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>parent=${cluster_woreda_id}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sub_kebele</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sub-Kebele</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>select_one agro_ecological_zone</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>cluster_agro_ecological_zone</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Agro Ecological Zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>remaining_land_area</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Remaining Land Area</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>${land_area} - ${actual_crop_area}</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cluster_area_timad</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Total Cultivated Area (Timad)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>One Timad is 0.25 hectare.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and (. * 0.25) &lt;= ${remaining_land_area}</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Total Cultivated Area cannot be negative or exceed the remaining available land area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cluster_area_hectare</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>if(${cluster_area_timad} != '', ${cluster_area_timad} * 0.25, 0)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>total_area_display</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Total Cultivated Area (ha): ${cluster_area_hectare}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cluster_plan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Actual Planned Area (ha)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${cluster_area_hectare}</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Planned Area (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>cluster_collected_land_quintal</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Actual Collected Land (quintals)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Actual Collected Land (quintals) cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>cluster_collected_quintal</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Actual Quantity Collected (quintals)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Actual Quantity Collected cannot be negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>cluster_collected_by_combiner</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Actual Area Collected by Combine Harvester (ha)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${cluster_plan}</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Actual Area Collected by Combine Harvester (ha) must be 0 or greater and cannot exceed Actual Planned Area (ha).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>select_one water_source</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>cluster_water_resource_id</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Water Source</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>select_one method</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>cluster_method_id</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Irrigation Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>select_one frequency</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>cluster_frequency</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Irrigation Frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>actual_growth_duration</t>
-        </is>
-      </c>
-      <c r="C31" s="39" t="inlineStr">
-        <is>
-          <t>Actual Growth Duration (days)</t>
-        </is>
-      </c>
-      <c r="F31" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G31" s="39" t="inlineStr">
-        <is>
-          <t>Growth Duration cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t>actual_crop_area</t>
-        </is>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>Actual Crop Area (ha)</t>
-        </is>
-      </c>
-      <c r="E32" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F32" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${land_area}</t>
-        </is>
-      </c>
-      <c r="G32" s="39" t="inlineStr">
-        <is>
-          <t>concat('Actual crop area cannot exceed total land area of ', ${land_area}, ' ha')</t>
-        </is>
-      </c>
-      <c r="O32" s="39" t="inlineStr">
-        <is>
-          <t>Enter the actual crop area (ha).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>actual_yield</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="inlineStr">
-        <is>
-          <t>Actual Yield (quintals)</t>
-        </is>
-      </c>
-      <c r="F33" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G33" s="39" t="inlineStr">
-        <is>
-          <t>Actual Yield cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="39" t="inlineStr">
-        <is>
-          <t>select_one cult_method</t>
-        </is>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>cultivated_by</t>
-        </is>
-      </c>
-      <c r="C34" s="39" t="inlineStr">
-        <is>
-          <t>Cultivation Type</t>
-        </is>
-      </c>
-      <c r="K34" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="39" t="inlineStr">
-        <is>
-          <t>select_multiple land_prep_method</t>
-        </is>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>land_prep_method_ids</t>
-        </is>
-      </c>
-      <c r="C35" s="39" t="inlineStr">
-        <is>
-          <t>Land Preparation Methods</t>
-        </is>
-      </c>
-      <c r="K35" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="inlineStr">
-        <is>
-          <t>select_one seed_class</t>
-        </is>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>actual_seed_class</t>
-        </is>
-      </c>
-      <c r="C36" s="39" t="inlineStr">
-        <is>
-          <t>Seed Type</t>
-        </is>
-      </c>
-      <c r="K36" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="39" t="inlineStr">
-        <is>
-          <t>select_one seed_source</t>
-        </is>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>actual_seed_source</t>
-        </is>
-      </c>
-      <c r="C37" s="39" t="inlineStr">
-        <is>
-          <t>Seed Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file seed_variety.csv</t>
-        </is>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>seed_variety</t>
-        </is>
-      </c>
-      <c r="C38" s="39" t="inlineStr">
-        <is>
-          <t>Seed Variety</t>
-        </is>
-      </c>
-      <c r="K38" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>actual_seed_qty</t>
-        </is>
-      </c>
-      <c r="C39" s="39" t="inlineStr">
-        <is>
-          <t>Actual Seed Quantity (kg)</t>
-        </is>
-      </c>
-      <c r="F39" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G39" s="39" t="inlineStr">
-        <is>
-          <t>Actual Seed Quantity cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="inlineStr">
-        <is>
-          <t>select_one fertilizer_type</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>actual_fertilizer_type</t>
-        </is>
-      </c>
-      <c r="C40" s="39" t="inlineStr">
-        <is>
-          <t>Actual Fertilizer Type</t>
-        </is>
-      </c>
-      <c r="K40" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>actual_fertilizer_qty</t>
-        </is>
-      </c>
-      <c r="C41" s="39" t="inlineStr">
-        <is>
-          <t>Actual Fertilizer Quantity (kg)</t>
-        </is>
-      </c>
-      <c r="F41" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G41" s="39" t="inlineStr">
-        <is>
-          <t>Actual Fertilizer Quantity cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="39" t="inlineStr">
-        <is>
-          <t>select_one water_source</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>water_resource_id</t>
-        </is>
-      </c>
-      <c r="C42" s="39" t="inlineStr">
-        <is>
-          <t>Water Source</t>
-        </is>
-      </c>
-      <c r="E42" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K42" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="O42" s="39" t="inlineStr">
-        <is>
-          <t>Select the water source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="39" t="inlineStr">
-        <is>
-          <t>select_one method</t>
-        </is>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>method_id</t>
-        </is>
-      </c>
-      <c r="C43" s="39" t="inlineStr">
-        <is>
-          <t>Irrigation Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t>select_one frequency</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>Irrigation Frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>cluster_smallholders</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Number of Smallholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>surveyor_name</t>
-        </is>
-      </c>
-      <c r="C45" s="39" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>cluster_surveyor_name</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>Development Agent Name</t>
         </is>
       </c>
-      <c r="F45" s="39" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G45" s="39" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>surveyor_mobile_number</t>
-        </is>
-      </c>
-      <c r="C46" s="39" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>cluster_surveyor_mobile_number</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>Development Agent Mobile Number</t>
         </is>
       </c>
-      <c r="D46" s="39" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
-      <c r="F46" s="39" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G46" s="39" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="39" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
-        <is>
-          <t>supervisor_name</t>
-        </is>
-      </c>
-      <c r="C47" s="39" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>cluster_supervisor_name</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>Supervisor Name</t>
         </is>
       </c>
-      <c r="F47" s="39" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G47" s="39" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="39" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B48" s="39" t="inlineStr">
-        <is>
-          <t>supervisor_mobile_number</t>
-        </is>
-      </c>
-      <c r="C48" s="39" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>cluster_supervisor_mobile_number</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>Supervisor Mobile Number</t>
         </is>
       </c>
-      <c r="D48" s="39" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
-      <c r="F48" s="39" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G48" s="39" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>begin_repeat</t>
-        </is>
-      </c>
-      <c r="B49" s="39" t="inlineStr">
-        <is>
-          <t>cluster_information</t>
-        </is>
-      </c>
-      <c r="C49" s="39" t="inlineStr">
-        <is>
-          <t>Cluster Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B50" s="39" t="inlineStr">
-        <is>
-          <t>cluster_land_info_id</t>
-        </is>
-      </c>
-      <c r="C50" s="39" t="inlineStr">
-        <is>
-          <t>Land ID</t>
-        </is>
-      </c>
-      <c r="E50" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F50" s="39" t="inlineStr">
-        <is>
-          <t>. = ${land_info_id}</t>
-        </is>
-      </c>
-      <c r="G50" s="39" t="inlineStr">
-        <is>
-          <t>Land ID does not match the Land ID provided in Cultivation / Land Preparation. Please enter the correct Land ID.</t>
-        </is>
-      </c>
-      <c r="O50" s="39" t="inlineStr">
-        <is>
-          <t>Enter the Land ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B51" s="39" t="inlineStr">
-        <is>
-          <t>cluster_name</t>
-        </is>
-      </c>
-      <c r="C51" s="39" t="inlineStr">
-        <is>
-          <t>Farmer Production Cluster (FPC) Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="39" t="inlineStr">
-        <is>
-          <t>select_one crop_season</t>
-        </is>
-      </c>
-      <c r="B52" s="39" t="inlineStr">
-        <is>
-          <t>cluster_season_id</t>
-        </is>
-      </c>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>Season</t>
-        </is>
-      </c>
-      <c r="F52" s="39" t="inlineStr">
-        <is>
-          <t>. = ${production_season}</t>
-        </is>
-      </c>
-      <c r="G52" s="39" t="inlineStr">
-        <is>
-          <t>Season must match the Production Season selected earlier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="39" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B53" s="39" t="inlineStr">
-        <is>
-          <t>cluster_start_gc</t>
-        </is>
-      </c>
-      <c r="C53" s="39" t="inlineStr">
-        <is>
-          <t>Start Date (Gregorian calendar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="39" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>cluster_end_gc</t>
-        </is>
-      </c>
-      <c r="C54" s="39" t="inlineStr">
-        <is>
-          <t>End Date (Gregorian calendar)</t>
-        </is>
-      </c>
-      <c r="F54" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= ${cluster_start_gc}</t>
-        </is>
-      </c>
-      <c r="G54" s="39" t="inlineStr">
-        <is>
-          <t>End date cannot be before Start date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B55" s="39" t="inlineStr">
-        <is>
-          <t>cluster_start_month</t>
-        </is>
-      </c>
-      <c r="C55" s="39" t="inlineStr">
-        <is>
-          <t>Start Month</t>
-        </is>
-      </c>
-      <c r="I55" s="39" t="inlineStr">
-        <is>
-          <t>format-date(${cluster_start_gc}, '%m')</t>
-        </is>
-      </c>
-      <c r="J55" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B56" s="39" t="inlineStr">
-        <is>
-          <t>cluster_start_day</t>
-        </is>
-      </c>
-      <c r="C56" s="39" t="inlineStr">
-        <is>
-          <t>Start Day</t>
-        </is>
-      </c>
-      <c r="I56" s="39" t="inlineStr">
-        <is>
-          <t>format-date(${cluster_start_gc}, '%d')</t>
-        </is>
-      </c>
-      <c r="J56" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B57" s="39" t="inlineStr">
-        <is>
-          <t>cluster_end_month</t>
-        </is>
-      </c>
-      <c r="C57" s="39" t="inlineStr">
-        <is>
-          <t>End Month</t>
-        </is>
-      </c>
-      <c r="I57" s="39" t="inlineStr">
-        <is>
-          <t>format-date(${cluster_end_gc}, '%m')</t>
-        </is>
-      </c>
-      <c r="J57" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B58" s="39" t="inlineStr">
-        <is>
-          <t>cluster_end_day</t>
-        </is>
-      </c>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>End Day</t>
-        </is>
-      </c>
-      <c r="I58" s="39" t="inlineStr">
-        <is>
-          <t>format-date(${cluster_end_gc}, '%d')</t>
-        </is>
-      </c>
-      <c r="J58" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file region.csv</t>
-        </is>
-      </c>
-      <c r="B59" s="39" t="inlineStr">
-        <is>
-          <t>cluster_region_id</t>
-        </is>
-      </c>
-      <c r="C59" s="39" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="K59" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file zone.csv</t>
-        </is>
-      </c>
-      <c r="B60" s="39" t="inlineStr">
-        <is>
-          <t>cluster_zone_id</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>Zone</t>
-        </is>
-      </c>
-      <c r="K60" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="M60" s="39" t="inlineStr">
-        <is>
-          <t>parent=${cluster_region_id}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file woreda.csv</t>
-        </is>
-      </c>
-      <c r="B61" s="39" t="inlineStr">
-        <is>
-          <t>cluster_woreda_id</t>
-        </is>
-      </c>
-      <c r="C61" s="39" t="inlineStr">
-        <is>
-          <t>Woreda</t>
-        </is>
-      </c>
-      <c r="K61" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="M61" s="39" t="inlineStr">
-        <is>
-          <t>parent=${cluster_zone_id}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="39" t="inlineStr">
-        <is>
-          <t>select_one_from_file kebele.csv</t>
-        </is>
-      </c>
-      <c r="B62" s="39" t="inlineStr">
-        <is>
-          <t>cluster_kebele_id</t>
-        </is>
-      </c>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>Kebele</t>
-        </is>
-      </c>
-      <c r="K62" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="M62" s="39" t="inlineStr">
-        <is>
-          <t>parent=${cluster_woreda_id}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B63" s="39" t="inlineStr">
-        <is>
-          <t>sub_kebele</t>
-        </is>
-      </c>
-      <c r="C63" s="39" t="inlineStr">
-        <is>
-          <t>Sub-Kebele</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="39" t="inlineStr">
-        <is>
-          <t>select_one agro_ecological_zone</t>
-        </is>
-      </c>
-      <c r="B64" s="39" t="inlineStr">
-        <is>
-          <t>cluster_agro_ecological_zone</t>
-        </is>
-      </c>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>Agro Ecological Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B65" s="39" t="inlineStr">
-        <is>
-          <t>remaining_land_area</t>
-        </is>
-      </c>
-      <c r="C65" s="39" t="inlineStr">
-        <is>
-          <t>Remaining Land Area</t>
-        </is>
-      </c>
-      <c r="I65" s="39" t="inlineStr">
-        <is>
-          <t>${land_area} - ${actual_crop_area}</t>
-        </is>
-      </c>
-      <c r="J65" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B66" s="39" t="inlineStr">
-        <is>
-          <t>cluster_area_timad</t>
-        </is>
-      </c>
-      <c r="C66" s="39" t="inlineStr">
-        <is>
-          <t>Total Cultivated Area (Timad)</t>
-        </is>
-      </c>
-      <c r="D66" s="39" t="inlineStr">
-        <is>
-          <t>One Timad is 0.25 hectare.</t>
-        </is>
-      </c>
-      <c r="F66" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and (. * 0.25) &lt;= ${remaining_land_area}</t>
-        </is>
-      </c>
-      <c r="G66" s="39" t="inlineStr">
-        <is>
-          <t>Total Cultivated Area cannot be negative or exceed the remaining available land area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="39" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B67" s="39" t="inlineStr">
-        <is>
-          <t>cluster_area_hectare</t>
-        </is>
-      </c>
-      <c r="I67" s="39" t="inlineStr">
-        <is>
-          <t>if(${cluster_area_timad} != '', ${cluster_area_timad} * 0.25, 0)</t>
-        </is>
-      </c>
-      <c r="J67" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="39" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B68" s="39" t="inlineStr">
-        <is>
-          <t>total_area_display</t>
-        </is>
-      </c>
-      <c r="C68" s="39" t="inlineStr">
-        <is>
-          <t>Total Cultivated Area (ha): ${cluster_area_hectare}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B69" s="39" t="inlineStr">
-        <is>
-          <t>cluster_plan</t>
-        </is>
-      </c>
-      <c r="C69" s="39" t="inlineStr">
-        <is>
-          <t>Actual Planned Area (ha)</t>
-        </is>
-      </c>
-      <c r="F69" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${cluster_area_hectare}</t>
-        </is>
-      </c>
-      <c r="G69" s="39" t="inlineStr">
-        <is>
-          <t>Planned Area (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B70" s="39" t="inlineStr">
-        <is>
-          <t>cluster_collected_land_quintal</t>
-        </is>
-      </c>
-      <c r="C70" s="39" t="inlineStr">
-        <is>
-          <t>Actual Collected Land (quintals)</t>
-        </is>
-      </c>
-      <c r="F70" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G70" s="39" t="inlineStr">
-        <is>
-          <t>Actual Collected Land (quintals) cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B71" s="39" t="inlineStr">
-        <is>
-          <t>cluster_collected_quintal</t>
-        </is>
-      </c>
-      <c r="C71" s="39" t="inlineStr">
-        <is>
-          <t>Actual Quantity Collected (quintals)</t>
-        </is>
-      </c>
-      <c r="F71" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="G71" s="39" t="inlineStr">
-        <is>
-          <t>Actual Quantity Collected cannot be negative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="39" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="B72" s="39" t="inlineStr">
-        <is>
-          <t>cluster_collected_by_combiner</t>
-        </is>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>Actual Area Collected by Combine Harvester (ha)</t>
-        </is>
-      </c>
-      <c r="F72" s="39" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${cluster_plan}</t>
-        </is>
-      </c>
-      <c r="G72" s="39" t="inlineStr">
-        <is>
-          <t>Actual Area Collected by Combine Harvester (ha) must be 0 or greater and cannot exceed Actual Planned Area (ha).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="39" t="inlineStr">
-        <is>
-          <t>select_one water_source</t>
-        </is>
-      </c>
-      <c r="B73" s="39" t="inlineStr">
-        <is>
-          <t>cluster_water_resource_id</t>
-        </is>
-      </c>
-      <c r="C73" s="39" t="inlineStr">
-        <is>
-          <t>Water Source</t>
-        </is>
-      </c>
-      <c r="E73" s="39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K73" s="39" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="O73" s="39" t="inlineStr">
-        <is>
-          <t>Select the water source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="39" t="inlineStr">
-        <is>
-          <t>select_one method</t>
-        </is>
-      </c>
-      <c r="B74" s="39" t="inlineStr">
-        <is>
-          <t>cluster_method_id</t>
-        </is>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>Irrigation Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="39" t="inlineStr">
-        <is>
-          <t>select_one frequency</t>
-        </is>
-      </c>
-      <c r="B75" s="39" t="inlineStr">
-        <is>
-          <t>cluster_frequency</t>
-        </is>
-      </c>
-      <c r="C75" s="39" t="inlineStr">
-        <is>
-          <t>Irrigation Frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="39" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B76" s="39" t="inlineStr">
-        <is>
-          <t>cluster_smallholders</t>
-        </is>
-      </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>Number of Smallholders</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B77" s="39" t="inlineStr">
-        <is>
-          <t>cluster_surveyor_name</t>
-        </is>
-      </c>
-      <c r="C77" s="39" t="inlineStr">
-        <is>
-          <t>Development Agent Name</t>
-        </is>
-      </c>
-      <c r="F77" s="39" t="inlineStr">
-        <is>
-          <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
-        </is>
-      </c>
-      <c r="G77" s="39" t="inlineStr">
-        <is>
-          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B78" s="39" t="inlineStr">
-        <is>
-          <t>cluster_surveyor_mobile_number</t>
-        </is>
-      </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>Development Agent Mobile Number</t>
-        </is>
-      </c>
-      <c r="D78" s="39" t="inlineStr">
-        <is>
-          <t>For example 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F78" s="39" t="inlineStr">
-        <is>
-          <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
-        </is>
-      </c>
-      <c r="G78" s="39" t="inlineStr">
-        <is>
-          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B79" s="39" t="inlineStr">
-        <is>
-          <t>cluster_supervisor_name</t>
-        </is>
-      </c>
-      <c r="C79" s="39" t="inlineStr">
-        <is>
-          <t>Supervisor Name</t>
-        </is>
-      </c>
-      <c r="F79" s="39" t="inlineStr">
-        <is>
-          <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
-        </is>
-      </c>
-      <c r="G79" s="39" t="inlineStr">
-        <is>
-          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
-      <c r="A80" s="39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B80" s="39" t="inlineStr">
-        <is>
-          <t>cluster_supervisor_mobile_number</t>
-        </is>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>Supervisor Mobile Number</t>
-        </is>
-      </c>
-      <c r="D80" s="39" t="inlineStr">
-        <is>
-          <t>For example 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F80" s="39" t="inlineStr">
-        <is>
-          <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
-        </is>
-      </c>
-      <c r="G80" s="39" t="inlineStr">
-        <is>
-          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="39" t="inlineStr">
-        <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="39" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
@@ -2699,1130 +2677,1130 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="G1" s="39" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="H1" s="39" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>yes_only</t>
         </is>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>cropping_sys</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>mono_cropping</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Mono-cropping</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>cropping_sys</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>inter_cropping</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Inter-cropping</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>government</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Government / Woreda Agriculture Office</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>cooperative</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Agricultural Cooperative / Union</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>private</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Private Seed Enterprise</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Farmer-to-Farmer Exchange / Saved Seed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>seed_class</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>seed_class</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>improved</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Improved</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>rainfed</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Rainfed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>river</t>
         </is>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>River</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>pond</t>
         </is>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Pond</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>well</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Well</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>borehole</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Borehole</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>irrigation_scheme</t>
         </is>
       </c>
-      <c r="C17" s="39" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Irrigation Scheme</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>water_source</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>water_harvesting_structure</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Water Harvesting Structure</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>surface_flood</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Surface / Flood</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>sprinkler</t>
         </is>
       </c>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Sprinkler</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>drip</t>
         </is>
       </c>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Drip</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>bi-weekly</t>
         </is>
       </c>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Every two weeks</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="C27" s="39" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>as_needed</t>
         </is>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>As Needed</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>urea</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Urea</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>nps</t>
         </is>
       </c>
-      <c r="C31" s="39" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>NPS</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>npsb</t>
         </is>
       </c>
-      <c r="C32" s="39" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>NPSB</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B33" s="39" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>dap</t>
         </is>
       </c>
-      <c r="C33" s="39" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>DAP</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>compost</t>
         </is>
       </c>
-      <c r="C34" s="39" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Compost</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>manure</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Manure</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>blended</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Blended</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B37" s="39" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C37" s="39" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>oxen_tillage</t>
         </is>
       </c>
-      <c r="C38" s="39" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Oxen Tillage</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>equine_other</t>
         </is>
       </c>
-      <c r="C39" s="39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Equine/Other Animals</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B40" s="39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>tractor_ploughing</t>
         </is>
       </c>
-      <c r="C40" s="39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Tractor Ploughing</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>power_tiller</t>
         </is>
       </c>
-      <c r="C41" s="39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Power Tiller</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B42" s="39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>combine_harvester</t>
         </is>
       </c>
-      <c r="C42" s="39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Combine Harvester</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B43" s="39" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>thrashing_machine</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Threshing Machine</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>family_labor</t>
         </is>
       </c>
-      <c r="C44" s="39" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Family Labour</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>debo_jigi</t>
         </is>
       </c>
-      <c r="C45" s="39" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Debo / Jigi</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>hired_labor</t>
         </is>
       </c>
-      <c r="C46" s="39" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Hired Labour</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>tractor_oxen</t>
         </is>
       </c>
-      <c r="C47" s="39" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Tractor Primary Tillage + Oxen Secondary Tillage</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>cult_method</t>
         </is>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>oxen_manual</t>
         </is>
       </c>
-      <c r="C48" s="39" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Oxen Ploughing + Manual Row Seeding</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B49" s="39" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>traditional_maresha_ploughing</t>
         </is>
       </c>
-      <c r="C49" s="39" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Traditional Maresha Ploughing</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>tractor_disc/moldboard_ploughing</t>
         </is>
       </c>
-      <c r="C50" s="39" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Tractor Disc / Moldboard Ploughing</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B51" s="39" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>manual_digging</t>
         </is>
       </c>
-      <c r="C51" s="39" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Manual Digging</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="39" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>shilshalo</t>
         </is>
       </c>
-      <c r="C52" s="39" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Shilshalo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>ridging_furrowing</t>
         </is>
       </c>
-      <c r="C53" s="39" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ridging / Furrowing</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B54" s="39" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>manual_leveling</t>
         </is>
       </c>
-      <c r="C54" s="39" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Manual Levelling</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="39" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B55" s="39" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>minimum_tillage</t>
         </is>
       </c>
-      <c r="C55" s="39" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Minimum Tillage</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="39" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>soil_water_conservation_structures</t>
         </is>
       </c>
-      <c r="C56" s="39" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Soil &amp; Water Conservation Structures</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>land_prep_method</t>
         </is>
       </c>
-      <c r="B57" s="39" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>biological_mulching</t>
         </is>
       </c>
-      <c r="C57" s="39" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Biological Mulching</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="39" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>SEASON_MEHER</t>
         </is>
       </c>
-      <c r="C58" s="39" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Meher (main rains)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>SEASON_BELG</t>
         </is>
       </c>
-      <c r="C59" s="39" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Belg (short rains)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="39" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B60" s="39" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>SEASON_IRRIGATION</t>
         </is>
       </c>
-      <c r="C60" s="39" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Irrigation (dry season)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="39" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B61" s="39" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>AEZ_BEREHA</t>
         </is>
       </c>
-      <c r="C61" s="39" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Bereha (hot lowland)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B62" s="39" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>AEZ_KOLLA</t>
         </is>
       </c>
-      <c r="C62" s="39" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Kolla (lowland)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B63" s="39" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>AEZ_WEYNA_DEGA</t>
         </is>
       </c>
-      <c r="C63" s="39" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Weyna Dega (midland)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="39" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B64" s="39" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>AEZ_DEGA</t>
         </is>
       </c>
-      <c r="C64" s="39" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Dega (highland)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B65" s="39" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>AEZ_WURCH</t>
         </is>
       </c>
-      <c r="C65" s="39" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Wurch (cold highland)</t>
         </is>
@@ -3843,64 +3821,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>style</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>allow_choice_duplicates</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Crop Sown Registry - 2. Cultivation and Land Preparation</t>
         </is>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>crop_sown_registry_prep</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
-        <is>
-          <t>2026.10.31.1</t>
-        </is>
-      </c>
-      <c r="D2" s="39" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026.10.31.2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>English (en)</t>
         </is>
       </c>
-      <c r="E2" s="39" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="F2" s="39" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
